--- a/data/lsd/mic/2026-03-26 09.03.40 Run.xlsx
+++ b/data/lsd/mic/2026-03-26 09.03.40 Run.xlsx
@@ -72,7 +72,7 @@
     <t>File Exported</t>
   </si>
   <si>
-    <t>30/03/2026 12:08:54</t>
+    <t>16/04/2026 14:42:10</t>
   </si>
   <si>
     <t>Software Version</t>
@@ -194,7 +194,7 @@
     <t>30/03/2026 12:08:51</t>
   </si>
   <si>
-    <t xml:space="preserve">Cycling "18S2" _x000d_
+    <t xml:space="preserve">Cycling "18S2" 
 	Fluorescence Cutoff Level  changed from "7,00" to "5,00"</t>
   </si>
   <si>
